--- a/results/pr_AstroSync/exp/24EK/cv_scores/fair_cv_summary.xlsx
+++ b/results/pr_AstroSync/exp/24EK/cv_scores/fair_cv_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,38 +972,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1527525231651946</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7752525252525252</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="K10" t="n">
         <v>0.8000000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8015873015873015</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8133333333333335</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1766611862328474</v>
+        <v>0.2008836700853346</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6769506379307773</v>
+        <v>0.9953825822927396</v>
       </c>
     </row>
     <row r="11">
@@ -1024,43 +1024,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2081665999466133</v>
+        <v>0.1527525231651946</v>
       </c>
       <c r="I11" t="n">
         <v>0.7666666666666666</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7008547008547009</v>
+        <v>0.7752525252525252</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>0.875</v>
+        <v>0.8015873015873015</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9333333333333335</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1859700717810084</v>
+        <v>0.1766611862328474</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7273629294985328</v>
+        <v>0.6769506379307773</v>
       </c>
     </row>
     <row r="12">
@@ -1086,38 +1086,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="G12" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2081665999466133</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7008547008547009</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.7333333333333334</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.2309401076758503</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.7333333333333334</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.611111111111111</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.5333333333333333</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.875</v>
       </c>
       <c r="M12" t="n">
-        <v>0.84</v>
+        <v>0.9333333333333335</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2100295767484402</v>
+        <v>0.1859700717810084</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7661340083538208</v>
+        <v>0.7273629294985328</v>
       </c>
     </row>
     <row r="13">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1153,28 +1153,28 @@
         <v>0.7333333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05773502691896264</v>
+        <v>0.2309401076758503</v>
       </c>
       <c r="I13" t="n">
         <v>0.7333333333333334</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7135531135531136</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8083333333333332</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2344164274463263</v>
+        <v>0.2100295767484402</v>
       </c>
       <c r="O13" t="n">
-        <v>1.326377301941582</v>
+        <v>0.7661340083538208</v>
       </c>
     </row>
     <row r="14">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1225,13 +1225,13 @@
         <v>0.8083333333333332</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.9066666666666667</v>
       </c>
       <c r="N14" t="n">
-        <v>0.244969299579869</v>
+        <v>0.2344164274463263</v>
       </c>
       <c r="O14" t="n">
-        <v>1.516563921879852</v>
+        <v>1.326377301941582</v>
       </c>
     </row>
     <row r="15">
@@ -1257,38 +1257,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05773502691896255</v>
+        <v>0.05773502691896264</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="J15" t="n">
-        <v>0.722943722943723</v>
+        <v>0.7135531135531136</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.8083333333333332</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2331888242090203</v>
+        <v>0.244969299579869</v>
       </c>
       <c r="O15" t="n">
-        <v>1.053872993241043</v>
+        <v>1.516563921879852</v>
       </c>
     </row>
     <row r="16">
@@ -1309,43 +1309,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2645751311064591</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6680911680911681</v>
+        <v>0.7645687645687645</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.9333333333333335</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2373527270239806</v>
+        <v>0.2057797874085468</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9237185727943918</v>
+        <v>0.6945269791458571</v>
       </c>
     </row>
     <row r="17">
@@ -1366,43 +1366,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5666666666666668</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05773502691896264</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6654456654456654</v>
+        <v>0.7505827505827506</v>
       </c>
       <c r="K17" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5423280423280423</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.9066666666666667</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3336840233177842</v>
+        <v>0.221174609156863</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28721223892399</v>
+        <v>0.8113782225874909</v>
       </c>
     </row>
     <row r="18">
@@ -1423,43 +1423,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1154700538379251</v>
+        <v>0.1732050807568878</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6697746697746698</v>
+        <v>0.6141414141414141</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.8111111111111112</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3521403983217902</v>
+        <v>0.2335948817891443</v>
       </c>
       <c r="O18" t="n">
-        <v>1.182584670975617</v>
+        <v>1.104070267448452</v>
       </c>
     </row>
     <row r="19">
@@ -1480,43 +1480,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05773502691896255</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6483516483516484</v>
+        <v>0.6452991452991453</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3477106035441422</v>
+        <v>0.2505503349505286</v>
       </c>
       <c r="O19" t="n">
-        <v>1.319725355188528</v>
+        <v>1.793526887600885</v>
       </c>
     </row>
     <row r="20">
@@ -1537,43 +1537,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.05773502691896255</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6421356421356421</v>
+        <v>0.722943722943723</v>
       </c>
       <c r="K20" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6266666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3582374639227378</v>
+        <v>0.2331888242090203</v>
       </c>
       <c r="O20" t="n">
-        <v>1.188109974626957</v>
+        <v>1.053872993241043</v>
       </c>
     </row>
     <row r="21">
@@ -1594,43 +1594,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0577350269189626</v>
+        <v>0.05773502691896254</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6654456654456654</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.8933333333333334</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3708186975463416</v>
+        <v>0.3458823901501187</v>
       </c>
       <c r="O21" t="n">
-        <v>1.53191679254709</v>
+        <v>2.466892136650596</v>
       </c>
     </row>
     <row r="22">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1663,31 +1663,31 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09999999999999996</v>
+        <v>0.2645751311064591</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6626984126984127</v>
+        <v>0.6680911680911681</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="M22" t="n">
-        <v>0.68</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3017146816956666</v>
+        <v>0.2373527270239806</v>
       </c>
       <c r="O22" t="n">
-        <v>2.479247192267833</v>
+        <v>0.9237185727943918</v>
       </c>
     </row>
     <row r="23">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1708,43 +1708,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666668</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2081665999466133</v>
+        <v>0.05773502691896264</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4141414141414141</v>
+        <v>0.6654456654456654</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5423280423280423</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2252323086736227</v>
+        <v>0.3336840233177842</v>
       </c>
       <c r="O23" t="n">
-        <v>2.537155513721782</v>
+        <v>1.28721223892399</v>
       </c>
     </row>
     <row r="24">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1765,43 +1765,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.1154700538379251</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J24" t="n">
-        <v>0.557997557997558</v>
+        <v>0.6697746697746698</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L24" t="n">
-        <v>0.875</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8133333333333335</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2632105780972903</v>
+        <v>0.3521403983217902</v>
       </c>
       <c r="O24" t="n">
-        <v>2.801225330795268</v>
+        <v>1.182584670975617</v>
       </c>
     </row>
     <row r="25">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1827,38 +1827,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1527525231651947</v>
+        <v>0.05773502691896255</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4404761904761905</v>
+        <v>0.6483516483516484</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2652125272413892</v>
+        <v>0.3477106035441422</v>
       </c>
       <c r="O25" t="n">
-        <v>1.604693902712624</v>
+        <v>1.319725355188528</v>
       </c>
     </row>
     <row r="26">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1879,43 +1879,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0577350269189626</v>
+        <v>0.05773502691896255</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.492063492063492</v>
+        <v>0.6654456654456654</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7866666666666667</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3075538797117968</v>
+        <v>0.3488260320826659</v>
       </c>
       <c r="O26" t="n">
-        <v>3.548061746718614</v>
+        <v>1.537758638064488</v>
       </c>
     </row>
     <row r="27">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0577350269189626</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>0.492063492063492</v>
+        <v>0.6421356421356421</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.6266666666666666</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3086959273380802</v>
+        <v>0.3582374639227378</v>
       </c>
       <c r="O27" t="n">
-        <v>2.912920115523577</v>
+        <v>1.188109974626957</v>
       </c>
     </row>
     <row r="28">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1993,43 +1993,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1527525231651947</v>
+        <v>0.0577350269189626</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.6654456654456654</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2391687389100525</v>
+        <v>0.3708186975463416</v>
       </c>
       <c r="O28" t="n">
-        <v>2.949182532816215</v>
+        <v>1.53191679254709</v>
       </c>
     </row>
     <row r="29">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2050,43 +2050,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1527525231651947</v>
+        <v>0.1732050807568877</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.6300366300366301</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>0.4953703703703704</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7866666666666667</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2901089960413327</v>
+        <v>0.3853139721594319</v>
       </c>
       <c r="O29" t="n">
-        <v>1.376508173380679</v>
+        <v>1.361091292460405</v>
       </c>
     </row>
     <row r="30">
@@ -2107,43 +2107,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05773502691896258</v>
+        <v>0.09999999999999996</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4126984126984126</v>
+        <v>0.6626984126984127</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3040790925389253</v>
+        <v>0.3017146816956666</v>
       </c>
       <c r="O30" t="n">
-        <v>2.840495878554286</v>
+        <v>2.479247192267833</v>
       </c>
     </row>
     <row r="31">
@@ -2169,38 +2169,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H31" t="n">
         <v>0.2081665999466133</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4141414141414141</v>
       </c>
       <c r="K31" t="n">
         <v>0.4</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3216358220236538</v>
+        <v>0.2252323086736227</v>
       </c>
       <c r="O31" t="n">
-        <v>1.697953287253749</v>
+        <v>2.537155513721782</v>
       </c>
     </row>
     <row r="32">
@@ -2221,43 +2221,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09999999999999996</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.557997557997558</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.875</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8133333333333335</v>
       </c>
       <c r="N32" t="n">
-        <v>0.330997510496633</v>
+        <v>0.2632105780972903</v>
       </c>
       <c r="O32" t="n">
-        <v>4.052558467058563</v>
+        <v>2.801225330795268</v>
       </c>
     </row>
     <row r="33">
@@ -2278,43 +2278,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09999999999999995</v>
+        <v>0.1527525231651947</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3015873015873016</v>
+        <v>0.4404761904761905</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L33" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3343896178176125</v>
+        <v>0.2652125272413892</v>
       </c>
       <c r="O33" t="n">
-        <v>3.345091008771055</v>
+        <v>1.604693902712624</v>
       </c>
     </row>
     <row r="34">
@@ -2335,43 +2335,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09999999999999996</v>
+        <v>0.0577350269189626</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.492063492063492</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5238095238095238</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.64</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3502855655098414</v>
+        <v>0.3075538797117968</v>
       </c>
       <c r="O34" t="n">
-        <v>2.633101567094929</v>
+        <v>3.548061746718614</v>
       </c>
     </row>
     <row r="35">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2404,31 +2404,31 @@
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1732050807568878</v>
+        <v>0.0577350269189626</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J35" t="n">
-        <v>0.25</v>
+        <v>0.492063492063492</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3751009999414727</v>
+        <v>0.3086959273380802</v>
       </c>
       <c r="O35" t="n">
-        <v>3.789858972694241</v>
+        <v>2.912920115523577</v>
       </c>
     </row>
     <row r="36">
@@ -2449,43 +2449,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>3</v>
       </c>
       <c r="G36" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L36" t="n">
         <v>0.6</v>
       </c>
-      <c r="H36" t="n">
-        <v>0.1732050807568878</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="M36" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="N36" t="n">
-        <v>0.376999024616518</v>
+        <v>0.2391687389100525</v>
       </c>
       <c r="O36" t="n">
-        <v>2.783346144544255</v>
+        <v>2.949182532816215</v>
       </c>
     </row>
     <row r="37">
@@ -2511,38 +2511,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>0.05773502691896253</v>
+        <v>0.1154700538379251</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L37" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7733333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="N37" t="n">
-        <v>0.329273823842354</v>
+        <v>0.2751944599429949</v>
       </c>
       <c r="O37" t="n">
-        <v>2.783502308373938</v>
+        <v>3.349618562646285</v>
       </c>
     </row>
     <row r="38">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2575,31 +2575,31 @@
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1154700538379251</v>
+        <v>0.1527525231651947</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7866666666666667</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3398810118575865</v>
+        <v>0.2901089960413327</v>
       </c>
       <c r="O38" t="n">
-        <v>2.185317331612805</v>
+        <v>1.376508173380679</v>
       </c>
     </row>
     <row r="39">
@@ -2620,43 +2620,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1154700538379251</v>
+        <v>0.05773502691896258</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4126984126984126</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7600000000000001</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4045403310659803</v>
+        <v>0.3040790925389253</v>
       </c>
       <c r="O39" t="n">
-        <v>7.971090423404521</v>
+        <v>2.840495878554286</v>
       </c>
     </row>
     <row r="40">
@@ -2677,43 +2677,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H40" t="n">
         <v>0.1154700538379251</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4126984126984127</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L40" t="n">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7600000000000001</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4123051309878163</v>
+        <v>0.3061020502470533</v>
       </c>
       <c r="O40" t="n">
-        <v>4.447501989696664</v>
+        <v>2.641338302695677</v>
       </c>
     </row>
     <row r="41">
@@ -2739,37 +2739,949 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2081665999466133</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.3216358220236538</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.697953287253749</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3309084795912374</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.007659469272111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.09999999999999995</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3015873015873016</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.7866666666666667</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3027342995773013</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.035957993723267</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.09999999999999996</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.330997510496633</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4.052558467058563</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>(0, -2, -1)</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.09999999999999995</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.3015873015873016</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.3343896178176125</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.345091008771055</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.09999999999999996</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.4126984126984127</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.3502855655098414</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.633101567094929</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1732050807568878</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L47" t="n">
         <v>0.5</v>
       </c>
-      <c r="H41" t="n">
+      <c r="M47" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.3739541317980369</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.261269899417949</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.09999999999999996</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.4404761904761905</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.7733333333333334</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.3748641375893165</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.753575592935368</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1732050807568878</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.3751009999414727</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.789858972694241</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1732050807568878</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.376999024616518</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.783346144544255</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.05773502691896253</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.7733333333333334</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.329273823842354</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.783502308373938</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.3398810118575865</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.185317331612805</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.05773502691896253</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3703703703703704</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.3414908656506626</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3.60350402023541</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.4045403310659803</v>
+      </c>
+      <c r="O54" t="n">
+        <v>7.971090423404521</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.4123051309878163</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.447501989696664</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.3944444444444444</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.6444444444444445</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.3840188005972938</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.386358624039553</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>24EK</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I57" t="n">
         <v>0.5</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J57" t="n">
         <v>0.25</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K57" t="n">
         <v>0.2</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L57" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M57" t="n">
         <v>0.68</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N57" t="n">
         <v>0.3774346653238769</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O57" t="n">
         <v>2.00107083918202</v>
       </c>
     </row>
